--- a/artfynd/A 44952-2021 artfynd.xlsx
+++ b/artfynd/A 44952-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44952-2021 artfynd.xlsx
+++ b/artfynd/A 44952-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95683208</v>
+        <v>95999536</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489627.5228208077</v>
+        <v>489598</v>
       </c>
       <c r="R2" t="n">
-        <v>6608284.975027382</v>
+        <v>6608321</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,51 +765,55 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95683292</v>
+        <v>95683334</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489625.1045633153</v>
+        <v>489638</v>
       </c>
       <c r="R3" t="n">
-        <v>6608326.982437552</v>
+        <v>6608375</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -856,19 +854,9 @@
           <t>2021-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,19 +883,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95683334</v>
+        <v>95999537</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -928,20 +911,29 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489638.4168315291</v>
+        <v>489689</v>
       </c>
       <c r="R4" t="n">
-        <v>6608375.01814393</v>
+        <v>6608414</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,69 +973,78 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95683247</v>
+        <v>95999539</v>
       </c>
       <c r="B5" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Rågrecken, Vstm</t>
+          <t>Norr Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489627.0747375483</v>
+        <v>489684</v>
       </c>
       <c r="R5" t="n">
-        <v>6608306.229700867</v>
+        <v>6608391</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,22 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,78 +1084,69 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95999538</v>
+        <v>95683208</v>
       </c>
       <c r="B6" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489688.703569637</v>
+        <v>489627</v>
       </c>
       <c r="R6" t="n">
-        <v>6608412.83101923</v>
+        <v>6608285</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,58 +1186,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95999537</v>
+        <v>95999538</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1294,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489688.7063540208</v>
+        <v>489689</v>
       </c>
       <c r="R7" t="n">
-        <v>6608413.843048035</v>
+        <v>6608413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,19 +1279,9 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95999539</v>
+        <v>95683247</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,46 +1324,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>N Rågrecken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489684.0803027172</v>
+        <v>489627</v>
       </c>
       <c r="R8" t="n">
-        <v>6608390.578870736</v>
+        <v>6608306</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,22 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,83 +1394,69 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95999536</v>
+        <v>133016054</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr Rågrecken, Vstm</t>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489598</v>
+        <v>489591</v>
       </c>
       <c r="R9" t="n">
-        <v>6608321</v>
+        <v>6608282</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,12 +1480,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,24 +1506,326 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133017186</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stackafallsåsen, Stackafallsåsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489579</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6608344</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95999535</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr Rågrecken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489620</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6608226</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95683292</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Rågrecken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489625</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6608327</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44952-2021 artfynd.xlsx
+++ b/artfynd/A 44952-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999536</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683334</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999538</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683247</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133016054</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133017186</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1733,6 +1783,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95999535</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,8 +1881,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95683292</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>